--- a/data/sed/usgs/sed_2016_usgs.xlsx
+++ b/data/sed/usgs/sed_2016_usgs.xlsx
@@ -46,49 +46,49 @@
     <t>Sieve Size</t>
   </si>
   <si>
-    <t>Arsenic (mg/kg)</t>
+    <t>Arsenic (mg/kg As)</t>
   </si>
   <si>
     <t>As (mg/kg) USGS</t>
   </si>
   <si>
-    <t>Cadmium (mg/kg)</t>
+    <t>Cadmium (mg/kg Cd)</t>
   </si>
   <si>
     <t>Cd (mg/kg) USGS</t>
   </si>
   <si>
-    <t>Copper (mg/kg)</t>
+    <t>Copper (mg/kg Cu)</t>
   </si>
   <si>
     <t>Cu (mg/kg) USGS</t>
   </si>
   <si>
-    <t>Chromium (mg/kg)</t>
+    <t>Chromium (mg/kg Cr)</t>
   </si>
   <si>
     <t>Cr (mg/kg) USGS</t>
   </si>
   <si>
-    <t>Mercury (mg/kg)</t>
+    <t>Mercury (mg/kg Hg)</t>
   </si>
   <si>
     <t>Hg (mg/kg) USGS</t>
   </si>
   <si>
-    <t>Nickel (mg/kg)</t>
+    <t>Nickel (mg/kg Ni)</t>
   </si>
   <si>
     <t>Ni (mg/kg) USGS</t>
   </si>
   <si>
-    <t>Lead (mg/kg)</t>
+    <t>Lead (mg/kg Pb)</t>
   </si>
   <si>
     <t>Pb (mg/kg) USGS</t>
   </si>
   <si>
-    <t>Zinc (mg/kg)</t>
+    <t>Zinc (mg/kg Zn)</t>
   </si>
   <si>
     <t>Zn (mg/kg) USGS</t>
